--- a/elite-data/manifest-templates/EL_template_IndividualNonHumanTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_IndividualNonHumanTemplate.xlsx
@@ -146,7 +146,7 @@
     <t>Adult</t>
   </si>
   <si>
-    <t>Captive</t>
+    <t>captive</t>
   </si>
   <si>
     <t>ILO</t>
@@ -164,7 +164,7 @@
     <t>Juvenile</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>LC</t>
@@ -176,7 +176,7 @@
     <t>Acomys russatus</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>LG</t>
@@ -212,7 +212,7 @@
     <t>Anas carolinensis</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>Post-Juvenile</t>
@@ -221,7 +221,7 @@
     <t>Anas platyrhynchos</t>
   </si>
   <si>
-    <t>Wild</t>
+    <t>wild</t>
   </si>
   <si>
     <t>Reptile</t>
